--- a/documents/cuarto/segundo_cuatrimestre/metaheuristicas/trabajo_final/software/cec2017real/code/results_sca/results_cec2017_30.xlsx
+++ b/documents/cuarto/segundo_cuatrimestre/metaheuristicas/trabajo_final/software/cec2017real/code/results_sca/results_cec2017_30.xlsx
@@ -601,7 +601,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>535089316.6666667</v>
+        <v>543128181.8181819</v>
       </c>
       <c r="E2" t="n">
         <v>975369.3</v>
@@ -628,7 +628,7 @@
         <v>86.510178</v>
       </c>
       <c r="M2" t="n">
-        <v>1183.403466666667</v>
+        <v>1196.590834285714</v>
       </c>
       <c r="N2" t="n">
         <v>74.863823</v>
@@ -649,13 +649,13 @@
         <v>144.781354</v>
       </c>
       <c r="T2" t="n">
-        <v>66.09229400000001</v>
+        <v>66.092294</v>
       </c>
       <c r="U2" t="n">
-        <v>72266.20300000001</v>
+        <v>72266.20299999999</v>
       </c>
       <c r="V2" t="n">
-        <v>546.1316399999999</v>
+        <v>546.1316400000001</v>
       </c>
       <c r="W2" t="n">
         <v>90.14100499999999</v>
@@ -676,7 +676,7 @@
         <v>453.71321</v>
       </c>
       <c r="AC2" t="n">
-        <v>451.8834699999999</v>
+        <v>451.88347</v>
       </c>
       <c r="AD2" t="n">
         <v>401.03746</v>
@@ -685,7 +685,7 @@
         <v>473.4207</v>
       </c>
       <c r="AF2" t="n">
-        <v>336.27479</v>
+        <v>336.2747900000001</v>
       </c>
       <c r="AG2" t="n">
         <v>486408.58</v>
@@ -723,7 +723,7 @@
         <v>2506.1469</v>
       </c>
       <c r="K3" t="n">
-        <v>504.1602799999999</v>
+        <v>504.16028</v>
       </c>
       <c r="L3" t="n">
         <v>27667.335</v>
@@ -756,7 +756,7 @@
         <v>90921111</v>
       </c>
       <c r="V3" t="n">
-        <v>868655640</v>
+        <v>861797088.4615384</v>
       </c>
       <c r="W3" t="n">
         <v>1242.4415</v>
@@ -815,7 +815,7 @@
         <v>12869.9766</v>
       </c>
       <c r="H4" t="n">
-        <v>525.5347300000001</v>
+        <v>525.53473</v>
       </c>
       <c r="I4" t="n">
         <v>108.644687</v>
@@ -857,7 +857,7 @@
         <v>61762737</v>
       </c>
       <c r="V4" t="n">
-        <v>716881950</v>
+        <v>712519250</v>
       </c>
       <c r="W4" t="n">
         <v>1156.21471</v>
@@ -931,7 +931,7 @@
         <v>22441.517</v>
       </c>
       <c r="M5" t="n">
-        <v>8059.137299999999</v>
+        <v>8059.1373</v>
       </c>
       <c r="N5" t="n">
         <v>14269.1968</v>
@@ -958,7 +958,7 @@
         <v>44656912</v>
       </c>
       <c r="V5" t="n">
-        <v>619492370</v>
+        <v>601256846.1538461</v>
       </c>
       <c r="W5" t="n">
         <v>1147.20861</v>
@@ -1032,7 +1032,7 @@
         <v>21694.586</v>
       </c>
       <c r="M6" t="n">
-        <v>7846.9907</v>
+        <v>7846.990699999999</v>
       </c>
       <c r="N6" t="n">
         <v>12407.821</v>
@@ -1059,7 +1059,7 @@
         <v>30539207</v>
       </c>
       <c r="V6" t="n">
-        <v>471218160</v>
+        <v>478724665.3846154</v>
       </c>
       <c r="W6" t="n">
         <v>1062.57321</v>
@@ -1121,13 +1121,13 @@
         <v>443.99103</v>
       </c>
       <c r="I7" t="n">
-        <v>88.27317600000001</v>
+        <v>88.27317599999999</v>
       </c>
       <c r="J7" t="n">
         <v>1736.7989</v>
       </c>
       <c r="K7" t="n">
-        <v>435.5341099999999</v>
+        <v>435.53411</v>
       </c>
       <c r="L7" t="n">
         <v>19257.801</v>
@@ -1136,7 +1136,7 @@
         <v>7800.7789</v>
       </c>
       <c r="N7" t="n">
-        <v>9459.101500000001</v>
+        <v>9459.101499999999</v>
       </c>
       <c r="O7" t="n">
         <v>5370736900</v>
@@ -1160,7 +1160,7 @@
         <v>21578147.9</v>
       </c>
       <c r="V7" t="n">
-        <v>308383440</v>
+        <v>303389807.6923077</v>
       </c>
       <c r="W7" t="n">
         <v>979.93475</v>
@@ -1234,10 +1234,10 @@
         <v>14636.511</v>
       </c>
       <c r="M8" t="n">
-        <v>7700.969900000001</v>
+        <v>7700.9699</v>
       </c>
       <c r="N8" t="n">
-        <v>5130.041999999999</v>
+        <v>5130.042</v>
       </c>
       <c r="O8" t="n">
         <v>4115504700</v>
@@ -1261,7 +1261,7 @@
         <v>17708970.6</v>
       </c>
       <c r="V8" t="n">
-        <v>236843780</v>
+        <v>235849938.4615385</v>
       </c>
       <c r="W8" t="n">
         <v>931.77537</v>
@@ -1326,7 +1326,7 @@
         <v>74.259987</v>
       </c>
       <c r="J9" t="n">
-        <v>826.1755300000001</v>
+        <v>826.17553</v>
       </c>
       <c r="K9" t="n">
         <v>345.47377</v>
@@ -1362,7 +1362,7 @@
         <v>10530437.4</v>
       </c>
       <c r="V9" t="n">
-        <v>148844587</v>
+        <v>147872375.6</v>
       </c>
       <c r="W9" t="n">
         <v>864.28819</v>
@@ -1463,7 +1463,7 @@
         <v>6901911.8</v>
       </c>
       <c r="V10" t="n">
-        <v>87453791</v>
+        <v>88524862</v>
       </c>
       <c r="W10" t="n">
         <v>833.37963</v>
@@ -1516,7 +1516,7 @@
         <v>3.8055417794e+36</v>
       </c>
       <c r="F11" t="n">
-        <v>66583.22099999999</v>
+        <v>66583.22100000001</v>
       </c>
       <c r="G11" t="n">
         <v>1573.5614</v>
@@ -1525,7 +1525,7 @@
         <v>318.25262</v>
       </c>
       <c r="I11" t="n">
-        <v>58.80855699999999</v>
+        <v>58.808557</v>
       </c>
       <c r="J11" t="n">
         <v>516.59727</v>
@@ -1537,7 +1537,7 @@
         <v>7919.1801</v>
       </c>
       <c r="M11" t="n">
-        <v>7540.900200000001</v>
+        <v>7540.9002</v>
       </c>
       <c r="N11" t="n">
         <v>1832.906</v>
@@ -1558,13 +1558,13 @@
         <v>2335.3493</v>
       </c>
       <c r="T11" t="n">
-        <v>952.9819100000001</v>
+        <v>952.98191</v>
       </c>
       <c r="U11" t="n">
         <v>5121656.6</v>
       </c>
       <c r="V11" t="n">
-        <v>74135785</v>
+        <v>74821827.2</v>
       </c>
       <c r="W11" t="n">
         <v>751.4706199999999</v>
@@ -1626,7 +1626,7 @@
         <v>306.29633</v>
       </c>
       <c r="I12" t="n">
-        <v>54.87339100000001</v>
+        <v>54.873391</v>
       </c>
       <c r="J12" t="n">
         <v>483.65057</v>
@@ -1665,7 +1665,7 @@
         <v>4419084.9</v>
       </c>
       <c r="V12" t="n">
-        <v>52520623</v>
+        <v>52118680.4</v>
       </c>
       <c r="W12" t="n">
         <v>737.4331500000001</v>
@@ -1715,7 +1715,7 @@
         <v>14424183000</v>
       </c>
       <c r="E13" t="n">
-        <v>4.43365749517e+34</v>
+        <v>4.433657495169999e+34</v>
       </c>
       <c r="F13" t="n">
         <v>47547.264</v>
@@ -1739,7 +1739,7 @@
         <v>5905.269</v>
       </c>
       <c r="M13" t="n">
-        <v>7390.0776</v>
+        <v>7390.077600000001</v>
       </c>
       <c r="N13" t="n">
         <v>1171.52808</v>
@@ -1760,13 +1760,13 @@
         <v>2213.1687</v>
       </c>
       <c r="T13" t="n">
-        <v>736.2152599999999</v>
+        <v>736.2152600000001</v>
       </c>
       <c r="U13" t="n">
         <v>3932829.2</v>
       </c>
       <c r="V13" t="n">
-        <v>42900491</v>
+        <v>42023715.2</v>
       </c>
       <c r="W13" t="n">
         <v>661.08691</v>
@@ -1867,7 +1867,7 @@
         <v>3572622.1</v>
       </c>
       <c r="V14" t="n">
-        <v>34511991</v>
+        <v>34185988.8</v>
       </c>
       <c r="W14" t="n">
         <v>599.5957500000001</v>
@@ -1932,7 +1932,7 @@
         <v>49.524378</v>
       </c>
       <c r="J15" t="n">
-        <v>446.9627400000001</v>
+        <v>446.96274</v>
       </c>
       <c r="K15" t="n">
         <v>248.61292</v>
@@ -1941,7 +1941,7 @@
         <v>5104.5114</v>
       </c>
       <c r="M15" t="n">
-        <v>7297.055</v>
+        <v>7297.054999999999</v>
       </c>
       <c r="N15" t="n">
         <v>1107.76393</v>
@@ -1968,7 +1968,7 @@
         <v>2968697.1</v>
       </c>
       <c r="V15" t="n">
-        <v>25303285</v>
+        <v>26351553.2</v>
       </c>
       <c r="W15" t="n">
         <v>578.7447</v>
@@ -2069,7 +2069,7 @@
         <v>2742559.9</v>
       </c>
       <c r="V16" t="n">
-        <v>22169735.8</v>
+        <v>23004311.44</v>
       </c>
       <c r="W16" t="n">
         <v>565.40473</v>
